--- a/Assets/06 Data/ExcelData/dt_usable_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_usable_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D78BE8-B69D-4233-93DF-07AB0B3B2089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603AFFD8-6664-4090-B9AB-8FDC89EB9D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6FC80BC-1448-478E-B3D9-69242C647A71}"/>
+    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{B6FC80BC-1448-478E-B3D9-69242C647A71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,10 +82,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>uint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -211,6 +207,10 @@
   </si>
   <si>
     <t>MaxStackSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -674,95 +674,95 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -771,7 +771,7 @@
         <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>10</v>
@@ -780,10 +780,10 @@
         <v>10</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -829,10 +829,10 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -867,10 +867,10 @@
         <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -905,10 +905,10 @@
         <v>1256</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>6</v>
@@ -943,10 +943,10 @@
         <v>105</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>5</v>
@@ -981,10 +981,10 @@
         <v>883</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -1019,10 +1019,10 @@
         <v>403</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>3</v>
@@ -1057,10 +1057,10 @@
         <v>133</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>2</v>
@@ -1095,13 +1095,13 @@
         <v>428</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
         <v>375</v>
@@ -1133,10 +1133,10 @@
         <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1</v>
@@ -1171,10 +1171,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>0</v>
